--- a/business_registration_forms/023_downline_application_form--business_registration_forms.xlsx
+++ b/business_registration_forms/023_downline_application_form--business_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'email',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'email', 'value': 'email'}</t>
+          <t>email</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'phone',_'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'phone', 'value': 'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both',_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'both', 'value': 'both'}</t>
+          <t>both</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'physical',_'value':_'physical'}</t>
+          <t>physical</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'physical', 'value': 'physical'}</t>
+          <t>physical</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'mailing',_'value':_'mailing'}</t>
+          <t>mailing</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'mailing', 'value': 'mailing'}</t>
+          <t>mailing</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both',_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'both', 'value': 'both'}</t>
+          <t>both</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'american',_'value':_'american'}</t>
+          <t>american</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'American', 'value': 'American'}</t>
+          <t>American</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'nigerian',_'value':_'nigerian'}</t>
+          <t>nigerian</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Nigerian', 'value': 'Nigerian'}</t>
+          <t>Nigerian</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'other', 'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'employed',_'value':_'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'employed', 'value': 'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'unemployed',_'value':_'unemployed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'unemployed', 'value': 'unemployed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'other', 'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'primary',_'value':_'primary'}</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'primary', 'value': 'primary'}</t>
+          <t>primary</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'secondary',_'value':_'secondary'}</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'secondary', 'value': 'secondary'}</t>
+          <t>secondary</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'tertiary',_'value':_'tertiary'}</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'tertiary', 'value': 'tertiary'}</t>
+          <t>tertiary</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'postgraduate',_'value':_'postgraduate'}</t>
+          <t>postgraduate</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'postgraduate', 'value': 'postgraduate'}</t>
+          <t>postgraduate</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'single',_'value':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'single', 'value': 'single'}</t>
+          <t>single</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'married',_'value':_'married'}</t>
+          <t>married</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'married', 'value': 'married'}</t>
+          <t>married</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'engaged',_'value':_'engaged'}</t>
+          <t>engaged</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'engaged', 'value': 'engaged'}</t>
+          <t>engaged</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'other', 'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'male',_'value':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'male', 'value': 'male'}</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'female',_'value':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'female', 'value': 'female'}</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'other', 'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'christian',_'value':_'christian'}</t>
+          <t>christian</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Christian', 'value': 'Christian'}</t>
+          <t>Christian</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'muslim',_'value':_'muslim'}</t>
+          <t>muslim</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Muslim', 'value': 'Muslim'}</t>
+          <t>Muslim</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'other', 'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'uploaded',_'value':_'uploaded'}</t>
+          <t>uploaded</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'uploaded', 'value': 'uploaded'}</t>
+          <t>uploaded</t>
         </is>
       </c>
     </row>
@@ -1590,29 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'uploaded',_'value':_'uploaded'}</t>
+          <t>upload</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'uploaded', 'value': 'uploaded'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>profile_picture_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'upload',_'value':_'upload'}</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'upload', 'value': 'upload'}</t>
+          <t>upload</t>
         </is>
       </c>
     </row>
